--- a/MASTER/master_bank_panel.xlsx
+++ b/MASTER/master_bank_panel.xlsx
@@ -18214,12 +18214,24 @@
       <c r="AJ68" t="n">
         <v>34.79023776487428</v>
       </c>
-      <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
-      <c r="AN68" t="inlineStr"/>
-      <c r="AO68" t="inlineStr"/>
-      <c r="AP68" t="inlineStr"/>
+      <c r="AK68" t="n">
+        <v>118.2692835820896</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>73.74696019900499</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>94.92859203980099</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>1.723004975124378</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>1997.657647058824</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0.74</v>
+      </c>
       <c r="AQ68" t="inlineStr"/>
       <c r="AR68" t="inlineStr"/>
       <c r="AS68" t="n">
@@ -18255,8 +18267,12 @@
       <c r="BC68" t="n">
         <v>2</v>
       </c>
-      <c r="BD68" t="inlineStr"/>
-      <c r="BE68" t="inlineStr"/>
+      <c r="BD68" t="n">
+        <v>119</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>2010</v>
+      </c>
       <c r="BF68" t="inlineStr"/>
       <c r="BG68" t="inlineStr"/>
       <c r="BH68" t="inlineStr"/>
@@ -18490,12 +18506,24 @@
       <c r="AJ69" t="n">
         <v>9.029001728182235</v>
       </c>
-      <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
-      <c r="AN69" t="inlineStr"/>
-      <c r="AO69" t="inlineStr"/>
-      <c r="AP69" t="inlineStr"/>
+      <c r="AK69" t="n">
+        <v>134.3796029547553</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>91.42263157894737</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>103.1738088642659</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>2.09028162511542</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2156.046074074074</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0.84</v>
+      </c>
       <c r="AQ69" t="inlineStr"/>
       <c r="AR69" t="inlineStr"/>
       <c r="AS69" t="n">
@@ -18531,8 +18559,12 @@
       <c r="BC69" t="n">
         <v>1</v>
       </c>
-      <c r="BD69" t="inlineStr"/>
-      <c r="BE69" t="inlineStr"/>
+      <c r="BD69" t="n">
+        <v>135</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>2166</v>
+      </c>
       <c r="BF69" t="n">
         <v>148</v>
       </c>
@@ -18776,13 +18808,23 @@
       <c r="AJ70" t="n">
         <v>8.923427439844437</v>
       </c>
-      <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
-      <c r="AN70" t="inlineStr"/>
-      <c r="AO70" t="inlineStr"/>
+      <c r="AK70" t="n">
+        <v>187.8380760626398</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>134.3202013422819</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>145.9607651006712</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>1.904259507829978</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>1817.394372294372</v>
+      </c>
       <c r="AP70" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.02</v>
@@ -18823,8 +18865,12 @@
       <c r="BC70" t="n">
         <v>3</v>
       </c>
-      <c r="BD70" t="inlineStr"/>
-      <c r="BE70" t="inlineStr"/>
+      <c r="BD70" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>2235</v>
+      </c>
       <c r="BF70" t="n">
         <v>163</v>
       </c>
@@ -19066,13 +19112,23 @@
       <c r="AJ71" t="n">
         <v>7.111801675652793</v>
       </c>
-      <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
-      <c r="AN71" t="inlineStr"/>
-      <c r="AO71" t="inlineStr"/>
+      <c r="AK71" t="n">
+        <v>200.1678660565724</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>137.7384234608985</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>165.0763311148087</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2.664284525790349</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1956.111991869919</v>
+      </c>
       <c r="AP71" t="n">
-        <v>3.99</v>
+        <v>3.39</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.8</v>
@@ -19113,8 +19169,12 @@
       <c r="BC71" t="n">
         <v>2</v>
       </c>
-      <c r="BD71" t="inlineStr"/>
-      <c r="BE71" t="inlineStr"/>
+      <c r="BD71" t="n">
+        <v>246</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>2404</v>
+      </c>
       <c r="BF71" t="n">
         <v>223</v>
       </c>
@@ -19356,13 +19416,23 @@
       <c r="AJ72" t="n">
         <v>8.297967245915586</v>
       </c>
-      <c r="AK72" t="inlineStr"/>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
-      <c r="AN72" t="inlineStr"/>
-      <c r="AO72" t="inlineStr"/>
+      <c r="AK72" t="n">
+        <v>231.7054450915142</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>160.4509567387687</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>192.220224625624</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>2.577832778702163</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>2094.059736842105</v>
+      </c>
       <c r="AP72" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.62</v>
@@ -19403,8 +19473,12 @@
       <c r="BC72" t="n">
         <v>1</v>
       </c>
-      <c r="BD72" t="inlineStr"/>
-      <c r="BE72" t="inlineStr"/>
+      <c r="BD72" t="n">
+        <v>266</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>2404</v>
+      </c>
       <c r="BF72" t="n">
         <v>240</v>
       </c>
@@ -19660,15 +19734,29 @@
       <c r="AJ73" t="n">
         <v>8.378398964125218</v>
       </c>
-      <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
-      <c r="AN73" t="inlineStr"/>
-      <c r="AO73" t="inlineStr"/>
-      <c r="AP73" t="inlineStr"/>
+      <c r="AK73" t="n">
+        <v>265.1071482098251</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>171.1040965861782</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>218.4121398834305</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>2.465503746877602</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>2376.072276119403</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>4.48</v>
+      </c>
       <c r="AQ73" t="inlineStr"/>
       <c r="AR73" t="inlineStr"/>
-      <c r="AS73" t="inlineStr"/>
+      <c r="AS73" t="n">
+        <v>11.81</v>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AU73" t="n">
         <v>78.34001199635642</v>
@@ -19697,8 +19785,12 @@
       <c r="BC73" t="n">
         <v>1</v>
       </c>
-      <c r="BD73" t="inlineStr"/>
-      <c r="BE73" t="inlineStr"/>
+      <c r="BD73" t="n">
+        <v>268</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>2402</v>
+      </c>
       <c r="BF73" t="n">
         <v>244</v>
       </c>
@@ -39423,10 +39515,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="39">
@@ -39436,10 +39528,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="40">
@@ -39449,10 +39541,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="41">
@@ -39462,10 +39554,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="42">
@@ -39475,10 +39567,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="43">
@@ -39488,10 +39580,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C43" t="n">
-        <v>43.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="44">
@@ -39527,10 +39619,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" t="n">
-        <v>76.8</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="47">
@@ -39670,10 +39762,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="58">
@@ -39683,10 +39775,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="59">

--- a/MASTER/master_bank_panel.xlsx
+++ b/MASTER/master_bank_panel.xlsx
@@ -1324,7 +1324,7 @@
         <v>9878.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1132.68</v>
+        <v>4719.759999999999</v>
       </c>
       <c r="W3" t="n">
         <v>3311.39</v>
@@ -1366,7 +1366,7 @@
         <v>5.876809114756854</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11.46611327630713</v>
+        <v>47.77810396315229</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
         <v>9766.34</v>
       </c>
       <c r="V4" t="n">
-        <v>872.3099999999999</v>
+        <v>5169.179999999999</v>
       </c>
       <c r="W4" t="n">
         <v>3823.92</v>
@@ -1652,7 +1652,7 @@
         <v>-36.90305425310556</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.931800449298304</v>
+        <v>52.92852798489505</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
         <v>9601.18</v>
       </c>
       <c r="V5" t="n">
-        <v>995.6900000000001</v>
+        <v>5103.5</v>
       </c>
       <c r="W5" t="n">
         <v>3620.73</v>
@@ -1944,7 +1944,7 @@
         <v>-40.54147553430947</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10.37049612651778</v>
+        <v>53.15492470717141</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
         <v>12220.28</v>
       </c>
       <c r="V6" t="n">
-        <v>994.42</v>
+        <v>5629.25</v>
       </c>
       <c r="W6" t="n">
         <v>4158.3</v>
@@ -2240,7 +2240,7 @@
         <v>118.9412200300738</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.137456752218442</v>
+        <v>46.06482011868795</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
@@ -2504,7 +2504,7 @@
         <v>11854.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1029.99</v>
+        <v>6013.07</v>
       </c>
       <c r="W7" t="n">
         <v>4547.4</v>
@@ -2546,7 +2546,7 @@
         <v>28.81563007982773</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.688474668632699</v>
+        <v>50.72321709503512</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
         <v>4241.34</v>
       </c>
       <c r="V9" t="n">
-        <v>564.38</v>
+        <v>1840.62</v>
       </c>
       <c r="W9" t="n">
         <v>1154.87</v>
@@ -3102,7 +3102,7 @@
         <v>18.19059355103718</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13.30664365507127</v>
+        <v>43.39713392465588</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
@@ -3326,7 +3326,7 @@
         <v>4644.37</v>
       </c>
       <c r="V10" t="n">
-        <v>545.03</v>
+        <v>2186.55</v>
       </c>
       <c r="W10" t="n">
         <v>1427.91</v>
@@ -3354,7 +3354,7 @@
         <v>34.53003631813996</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11.73528379521873</v>
+        <v>47.07958237608116</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
@@ -4204,7 +4204,7 @@
         <v>3054.09</v>
       </c>
       <c r="V15" t="n">
-        <v>523.02</v>
+        <v>1610.08</v>
       </c>
       <c r="W15" t="n">
         <v>940.52</v>
@@ -4246,7 +4246,7 @@
         <v>-21.77793245745963</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17.12523206585267</v>
+        <v>52.71881313255339</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
         <v>2985.7</v>
       </c>
       <c r="V21" t="n">
-        <v>540.46</v>
+        <v>1757.71</v>
       </c>
       <c r="W21" t="n">
         <v>1098.91</v>
@@ -5360,7 +5360,7 @@
         <v>-4.914783987316684</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18.10161771108953</v>
+        <v>58.87095153565328</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
@@ -5590,7 +5590,7 @@
         <v>2985.7</v>
       </c>
       <c r="V22" t="n">
-        <v>540.46</v>
+        <v>1757.71</v>
       </c>
       <c r="W22" t="n">
         <v>1098.91</v>
@@ -5626,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18.10161771108953</v>
+        <v>58.87095153565328</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
@@ -6486,7 +6486,7 @@
         <v>4973.98</v>
       </c>
       <c r="V27" t="n">
-        <v>650.05</v>
+        <v>2124.68</v>
       </c>
       <c r="W27" t="n">
         <v>1229.75</v>
@@ -6528,7 +6528,7 @@
         <v>-28.29221377928973</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13.06901113394103</v>
+        <v>42.71589350982513</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
@@ -6776,7 +6776,7 @@
         <v>6264.06</v>
       </c>
       <c r="V28" t="n">
-        <v>803.85</v>
+        <v>3002.38</v>
       </c>
       <c r="W28" t="n">
         <v>-1785.43</v>
@@ -6818,7 +6818,7 @@
         <v>11.15477127370672</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12.83273148724629</v>
+        <v>47.93025609588669</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
         <v>6911.06</v>
       </c>
       <c r="V29" t="n">
-        <v>901.91</v>
+        <v>3119.24</v>
       </c>
       <c r="W29" t="n">
         <v>1889.9</v>
@@ -7114,7 +7114,7 @@
         <v>-7.072661185375018</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13.05024120757163</v>
+        <v>45.13403153785382</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
@@ -7368,7 +7368,7 @@
         <v>7056.93</v>
       </c>
       <c r="V30" t="n">
-        <v>949.1</v>
+        <v>3282.95</v>
       </c>
       <c r="W30" t="n">
         <v>1987.32</v>
@@ -7410,7 +7410,7 @@
         <v>-29.13626217967978</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13.44919107884023</v>
+        <v>46.52093757483778</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
@@ -7674,7 +7674,7 @@
         <v>8174.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1073.94</v>
+        <v>3507.91</v>
       </c>
       <c r="W31" t="n">
         <v>-2035.65</v>
@@ -7716,7 +7716,7 @@
         <v>-2.547833395167831</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13.13713785223931</v>
+        <v>42.91105391665157</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
@@ -8228,7 +8228,7 @@
         <v>5306</v>
       </c>
       <c r="V33" t="n">
-        <v>724.3099999999999</v>
+        <v>2495.23</v>
       </c>
       <c r="W33" t="n">
         <v>1611.06</v>
@@ -8270,7 +8270,7 @@
         <v>-29.61959113598066</v>
       </c>
       <c r="AJ33" t="n">
-        <v>13.65077271013946</v>
+        <v>47.02657369016208</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
@@ -8514,7 +8514,7 @@
         <v>6807.08</v>
       </c>
       <c r="V34" t="n">
-        <v>592.22</v>
+        <v>2930.88</v>
       </c>
       <c r="W34" t="n">
         <v>2045.47</v>
@@ -8556,7 +8556,7 @@
         <v>40.00474324370109</v>
       </c>
       <c r="AJ34" t="n">
-        <v>8.700059349970914</v>
+        <v>43.05634721495855</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
         <v>8765.01</v>
       </c>
       <c r="V35" t="n">
-        <v>736.67</v>
+        <v>3176.08</v>
       </c>
       <c r="W35" t="n">
         <v>2129.93</v>
@@ -8848,7 +8848,7 @@
         <v>35.60216181334192</v>
       </c>
       <c r="AJ35" t="n">
-        <v>8.404668106482479</v>
+        <v>36.23589704974666</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
@@ -9098,7 +9098,7 @@
         <v>9505.48</v>
       </c>
       <c r="V36" t="n">
-        <v>817.12</v>
+        <v>3227.63</v>
       </c>
       <c r="W36" t="n">
         <v>2410.51</v>
@@ -9140,7 +9140,7 @@
         <v>10.1456818911877</v>
       </c>
       <c r="AJ36" t="n">
-        <v>8.596304447539735</v>
+        <v>33.95546568926557</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
@@ -9402,7 +9402,7 @@
         <v>11170.62</v>
       </c>
       <c r="V37" t="n">
-        <v>1010.65</v>
+        <v>3651.11</v>
       </c>
       <c r="W37" t="n">
         <v>2640.46</v>
@@ -9444,7 +9444,7 @@
         <v>30.69401576461628</v>
       </c>
       <c r="AJ37" t="n">
-        <v>9.047393967389453</v>
+        <v>32.68493601966587</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
@@ -9960,7 +9960,7 @@
         <v>11950.9</v>
       </c>
       <c r="V39" t="n">
-        <v>1369.43</v>
+        <v>4868.11</v>
       </c>
       <c r="W39" t="n">
         <v>3164.82</v>
@@ -10002,7 +10002,7 @@
         <v>43.19824248966877</v>
       </c>
       <c r="AJ39" t="n">
-        <v>11.45880226593813</v>
+        <v>40.73425432394212</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
@@ -10250,7 +10250,7 @@
         <v>13038.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1446.86</v>
+        <v>5384.72</v>
       </c>
       <c r="W40" t="n">
         <v>3290.73</v>
@@ -10292,7 +10292,7 @@
         <v>19.06461952150584</v>
       </c>
       <c r="AJ40" t="n">
-        <v>11.09647118012841</v>
+        <v>41.29728535798977</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
@@ -10546,7 +10546,7 @@
         <v>19857.19</v>
       </c>
       <c r="V41" t="n">
-        <v>1875.36</v>
+        <v>6900.549999999999</v>
       </c>
       <c r="W41" t="n">
         <v>4234.42</v>
@@ -10588,7 +10588,7 @@
         <v>34.98816346118944</v>
       </c>
       <c r="AJ41" t="n">
-        <v>9.444236571236917</v>
+        <v>34.75088872091167</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
@@ -10842,7 +10842,7 @@
         <v>20653.93</v>
       </c>
       <c r="V42" t="n">
-        <v>2245</v>
+        <v>8018.36</v>
       </c>
       <c r="W42" t="n">
         <v>4782.11</v>
@@ -10884,7 +10884,7 @@
         <v>-8.319092489797375</v>
       </c>
       <c r="AJ42" t="n">
-        <v>10.86960205636409</v>
+        <v>38.82244202435081</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -11134,7 +11134,7 @@
         <v>21249.17</v>
       </c>
       <c r="V43" t="n">
-        <v>2493.81</v>
+        <v>8039.400000000001</v>
       </c>
       <c r="W43" t="n">
         <v>4691.56</v>
@@ -11176,7 +11176,7 @@
         <v>-17.28975388801538</v>
       </c>
       <c r="AJ43" t="n">
-        <v>11.73603486630301</v>
+        <v>37.83394833774684</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
@@ -11954,7 +11954,7 @@
         <v>6579.2</v>
       </c>
       <c r="V46" t="n">
-        <v>758.71</v>
+        <v>2742.04</v>
       </c>
       <c r="W46" t="n">
         <v>1628.05</v>
@@ -11992,7 +11992,7 @@
         <v>-21.0456810132661</v>
       </c>
       <c r="AJ46" t="n">
-        <v>11.53194917315175</v>
+        <v>41.67740758754864</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
@@ -13230,7 +13230,7 @@
         <v>6672.39</v>
       </c>
       <c r="V51" t="n">
-        <v>884.1</v>
+        <v>3191.32</v>
       </c>
       <c r="W51" t="n">
         <v>2023.92</v>
@@ -13272,7 +13272,7 @@
         <v>70.10901934381231</v>
       </c>
       <c r="AJ51" t="n">
-        <v>13.25012476788677</v>
+        <v>47.82873902754486</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
@@ -13516,7 +13516,7 @@
         <v>7941.16</v>
       </c>
       <c r="V52" t="n">
-        <v>683.39</v>
+        <v>3551.59</v>
       </c>
       <c r="W52" t="n">
         <v>2332.99</v>
@@ -13558,7 +13558,7 @@
         <v>30.90631390398482</v>
       </c>
       <c r="AJ52" t="n">
-        <v>8.605669700648267</v>
+        <v>44.72381868643876</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
@@ -13810,7 +13810,7 @@
         <v>13057.68</v>
       </c>
       <c r="V53" t="n">
-        <v>1019.95</v>
+        <v>3980.230000000001</v>
       </c>
       <c r="W53" t="n">
         <v>2209.82</v>
@@ -13852,7 +13852,7 @@
         <v>-79.92410293781325</v>
       </c>
       <c r="AJ53" t="n">
-        <v>7.811111927999461</v>
+        <v>30.48190796527409</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
@@ -14104,7 +14104,7 @@
         <v>13636.42</v>
       </c>
       <c r="V54" t="n">
-        <v>1112.7</v>
+        <v>5821.09</v>
       </c>
       <c r="W54" t="n">
         <v>3857.07</v>
@@ -14146,7 +14146,7 @@
         <v>-99.10990114303367</v>
       </c>
       <c r="AJ54" t="n">
-        <v>8.159766272966072</v>
+        <v>42.68781689035686</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
@@ -14412,7 +14412,7 @@
         <v>15194.02</v>
       </c>
       <c r="V55" t="n">
-        <v>1051.55</v>
+        <v>6155.4</v>
       </c>
       <c r="W55" t="n">
         <v>4311.04</v>
@@ -14454,7 +14454,7 @@
         <v>39372.88503253796</v>
       </c>
       <c r="AJ55" t="n">
-        <v>6.920814899546005</v>
+        <v>40.51199090168369</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
@@ -14970,7 +14970,7 @@
         <v>4925.93</v>
       </c>
       <c r="V57" t="n">
-        <v>689.33</v>
+        <v>2393.53</v>
       </c>
       <c r="W57" t="n">
         <v>1518.14</v>
@@ -15012,7 +15012,7 @@
         <v>11.63331089936595</v>
       </c>
       <c r="AJ57" t="n">
-        <v>13.9939057193261</v>
+        <v>48.5904184590524</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
@@ -15260,7 +15260,7 @@
         <v>5757.05</v>
       </c>
       <c r="V58" t="n">
-        <v>560.05</v>
+        <v>2736.34</v>
       </c>
       <c r="W58" t="n">
         <v>1842.76</v>
@@ -15302,7 +15302,7 @@
         <v>24.49928923186271</v>
       </c>
       <c r="AJ58" t="n">
-        <v>9.728072537150103</v>
+        <v>47.5302455250519</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
@@ -15556,7 +15556,7 @@
         <v>7389</v>
       </c>
       <c r="V59" t="n">
-        <v>821.75</v>
+        <v>3052.26</v>
       </c>
       <c r="W59" t="n">
         <v>1884.06</v>
@@ -15598,7 +15598,7 @@
         <v>16.48630601332442</v>
       </c>
       <c r="AJ59" t="n">
-        <v>11.12126133441602</v>
+        <v>41.30816077953715</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
         <v>14914.98</v>
       </c>
       <c r="V60" t="n">
-        <v>1352.02</v>
+        <v>6924.900000000001</v>
       </c>
       <c r="W60" t="n">
         <v>4950.85</v>
@@ -15894,7 +15894,7 @@
         <v>27.79314207698098</v>
       </c>
       <c r="AJ60" t="n">
-        <v>9.064846215013363</v>
+        <v>46.42916048160977</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
@@ -16154,7 +16154,7 @@
         <v>14160.19</v>
       </c>
       <c r="V61" t="n">
-        <v>1387.83</v>
+        <v>6871.76</v>
       </c>
       <c r="W61" t="n">
         <v>4911.79</v>
@@ -16196,7 +16196,7 @@
         <v>39.0928577787822</v>
       </c>
       <c r="AJ61" t="n">
-        <v>9.800927812409297</v>
+        <v>48.52872736877118</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
@@ -16994,7 +16994,7 @@
         <v>6352.88</v>
       </c>
       <c r="V64" t="n">
-        <v>1096.38</v>
+        <v>3396.53</v>
       </c>
       <c r="W64" t="n">
         <v>1923.72</v>
@@ -17036,7 +17036,7 @@
         <v>4.92637498678048</v>
       </c>
       <c r="AJ64" t="n">
-        <v>17.25799952147688</v>
+        <v>53.46441299064362</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
         <v>6866.92</v>
       </c>
       <c r="V65" t="n">
-        <v>801.9400000000001</v>
+        <v>3338.12</v>
       </c>
       <c r="W65" t="n">
         <v>2120.53</v>
@@ -17332,7 +17332,7 @@
         <v>-3.62432262578114</v>
       </c>
       <c r="AJ65" t="n">
-        <v>11.67830701391599</v>
+        <v>48.61160462041206</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
@@ -17892,7 +17892,7 @@
         <v>7440.67</v>
       </c>
       <c r="V67" t="n">
-        <v>849.9</v>
+        <v>3736.38</v>
       </c>
       <c r="W67" t="n">
         <v>2465.78</v>
@@ -17934,7 +17934,7 @@
         <v>80.21814006888634</v>
       </c>
       <c r="AJ67" t="n">
-        <v>11.42235847040656</v>
+        <v>50.21563918303056</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
@@ -18462,7 +18462,7 @@
         <v>11659.65</v>
       </c>
       <c r="V69" t="n">
-        <v>1052.75</v>
+        <v>4606.11</v>
       </c>
       <c r="W69" t="n">
         <v>3411.79</v>
@@ -18504,7 +18504,7 @@
         <v>30.73162703133483</v>
       </c>
       <c r="AJ69" t="n">
-        <v>9.029001728182235</v>
+        <v>39.50470211369981</v>
       </c>
       <c r="AK69" t="n">
         <v>134.3796029547553</v>
@@ -18764,7 +18764,7 @@
         <v>11473.17</v>
       </c>
       <c r="V70" t="n">
-        <v>1023.8</v>
+        <v>4072.759999999999</v>
       </c>
       <c r="W70" t="n">
         <v>2658.93</v>
@@ -18806,7 +18806,7 @@
         <v>-5.997283298914413</v>
       </c>
       <c r="AJ70" t="n">
-        <v>8.923427439844437</v>
+        <v>35.49812301221021</v>
       </c>
       <c r="AK70" t="n">
         <v>187.8380760626398</v>
@@ -19068,7 +19068,7 @@
         <v>21496.1</v>
       </c>
       <c r="V71" t="n">
-        <v>1528.76</v>
+        <v>6557.070000000001</v>
       </c>
       <c r="W71" t="n">
         <v>4525.1</v>
@@ -19110,7 +19110,7 @@
         <v>50.49130408221762</v>
       </c>
       <c r="AJ71" t="n">
-        <v>7.111801675652793</v>
+        <v>30.50353319904541</v>
       </c>
       <c r="AK71" t="n">
         <v>200.1678660565724</v>
@@ -19372,7 +19372,7 @@
         <v>20311.36</v>
       </c>
       <c r="V72" t="n">
-        <v>1685.43</v>
+        <v>7025.990000000001</v>
       </c>
       <c r="W72" t="n">
         <v>4660.88</v>
@@ -19414,7 +19414,7 @@
         <v>-3.24483913978898</v>
       </c>
       <c r="AJ72" t="n">
-        <v>8.297967245915586</v>
+        <v>34.59143060829014</v>
       </c>
       <c r="AK72" t="n">
         <v>231.7054450915142</v>
@@ -19690,7 +19690,7 @@
         <v>21006.4</v>
       </c>
       <c r="V73" t="n">
-        <v>1760</v>
+        <v>7570</v>
       </c>
       <c r="W73" t="n">
         <v>5049</v>
@@ -19732,7 +19732,7 @@
         <v>-4.437068246327714</v>
       </c>
       <c r="AJ73" t="n">
-        <v>8.378398964125218</v>
+        <v>36.03663645365221</v>
       </c>
       <c r="AK73" t="n">
         <v>265.1071482098251</v>
@@ -20268,7 +20268,7 @@
         <v>8189</v>
       </c>
       <c r="V75" t="n">
-        <v>813.08</v>
+        <v>3343.72</v>
       </c>
       <c r="W75" t="n">
         <v>2353.46</v>
@@ -20310,7 +20310,7 @@
         <v>26.93397459803077</v>
       </c>
       <c r="AJ75" t="n">
-        <v>9.928929051166199</v>
+        <v>40.83184760043962</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
@@ -20560,7 +20560,7 @@
         <v>8069.86</v>
       </c>
       <c r="V76" t="n">
-        <v>787.73</v>
+        <v>3239.63</v>
       </c>
       <c r="W76" t="n">
         <v>2451.9</v>
@@ -20602,7 +20602,7 @@
         <v>-1.2815620536061</v>
       </c>
       <c r="AJ76" t="n">
-        <v>9.76138371669397</v>
+        <v>40.14481044280818</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
@@ -20858,7 +20858,7 @@
         <v>10625.89</v>
       </c>
       <c r="V77" t="n">
-        <v>916.77</v>
+        <v>5178.21</v>
       </c>
       <c r="W77" t="n">
         <v>3885.52</v>
@@ -20900,7 +20900,7 @@
         <v>17.59325141621739</v>
       </c>
       <c r="AJ77" t="n">
-        <v>8.627700832589081</v>
+        <v>48.73201209498687</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
@@ -21154,7 +21154,7 @@
         <v>10625.89</v>
       </c>
       <c r="V78" t="n">
-        <v>916.77</v>
+        <v>5178.21</v>
       </c>
       <c r="W78" t="n">
         <v>3885.52</v>
@@ -21196,7 +21196,7 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="n">
-        <v>8.627700832589081</v>
+        <v>48.73201209498687</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
@@ -21456,7 +21456,7 @@
         <v>11995.32</v>
       </c>
       <c r="V79" t="n">
-        <v>1081.65</v>
+        <v>5292.96</v>
       </c>
       <c r="W79" t="n">
         <v>3860.4</v>
@@ -21498,7 +21498,7 @@
         <v>-10.4593929450369</v>
       </c>
       <c r="AJ79" t="n">
-        <v>9.017266734026272</v>
+        <v>44.12520883144426</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -22002,7 +22002,7 @@
         <v>11354.37</v>
       </c>
       <c r="V81" t="n">
-        <v>1614.43</v>
+        <v>5330.52</v>
       </c>
       <c r="W81" t="n">
         <v>3347.94</v>
@@ -22044,7 +22044,7 @@
         <v>5.176308842228927</v>
       </c>
       <c r="AJ81" t="n">
-        <v>14.21857839756851</v>
+        <v>46.9468583461698</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -22290,7 +22290,7 @@
         <v>13817.52</v>
       </c>
       <c r="V82" t="n">
-        <v>2101.54</v>
+        <v>6987.01</v>
       </c>
       <c r="W82" t="n">
         <v>4500.75</v>
@@ -22332,7 +22332,7 @@
         <v>29.33478166146559</v>
       </c>
       <c r="AJ82" t="n">
-        <v>15.20924160051876</v>
+        <v>50.56631001800612</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -22584,7 +22584,7 @@
         <v>15026.71</v>
       </c>
       <c r="V83" t="n">
-        <v>2026.03</v>
+        <v>7767.95</v>
       </c>
       <c r="W83" t="n">
         <v>4961.1</v>
@@ -22626,7 +22626,7 @@
         <v>5.452996846922731</v>
       </c>
       <c r="AJ83" t="n">
-        <v>13.48285819051542</v>
+        <v>51.69428304665492</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -22878,7 +22878,7 @@
         <v>13272.43</v>
       </c>
       <c r="V84" t="n">
-        <v>2061.81</v>
+        <v>7351.91</v>
       </c>
       <c r="W84" t="n">
         <v>4468.6</v>
@@ -22920,7 +22920,7 @@
         <v>-84.217406075005</v>
       </c>
       <c r="AJ84" t="n">
-        <v>15.5345328624826</v>
+        <v>55.39234337645781</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -23182,7 +23182,7 @@
         <v>11654.96</v>
       </c>
       <c r="V85" t="n">
-        <v>1801.4</v>
+        <v>6427.879999999999</v>
       </c>
       <c r="W85" t="n">
         <v>3830.33</v>
@@ -23224,7 +23224,7 @@
         <v>-650.6999287241624</v>
       </c>
       <c r="AJ85" t="n">
-        <v>15.45608050134878</v>
+        <v>55.15145483124782</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -24018,7 +24018,7 @@
         <v>8067.25</v>
       </c>
       <c r="V88" t="n">
-        <v>722.55</v>
+        <v>3084.49</v>
       </c>
       <c r="W88" t="n">
         <v>1874.39</v>
@@ -24060,7 +24060,7 @@
         <v>6.715824437069529</v>
       </c>
       <c r="AJ88" t="n">
-        <v>8.956583718119557</v>
+        <v>38.23471443180762</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -24310,7 +24310,7 @@
         <v>14768.57</v>
       </c>
       <c r="V89" t="n">
-        <v>1184.02</v>
+        <v>4932.639999999999</v>
       </c>
       <c r="W89" t="n">
         <v>3036.3</v>
@@ -24352,7 +24352,7 @@
         <v>-2.021539919949444</v>
       </c>
       <c r="AJ89" t="n">
-        <v>8.017160767765599</v>
+        <v>33.3995776165194</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -24602,7 +24602,7 @@
         <v>17772.54</v>
       </c>
       <c r="V90" t="n">
-        <v>1566.47</v>
+        <v>6268.52</v>
       </c>
       <c r="W90" t="n">
         <v>3768.83</v>
@@ -24644,7 +24644,7 @@
         <v>10.42939344178584</v>
       </c>
       <c r="AJ90" t="n">
-        <v>8.813990571972267</v>
+        <v>35.27081666435974</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
@@ -24908,7 +24908,7 @@
         <v>17652.48</v>
       </c>
       <c r="V91" t="n">
-        <v>1610.78</v>
+        <v>6546.1</v>
       </c>
       <c r="W91" t="n">
         <v>-3996.51</v>
@@ -24950,7 +24950,7 @@
         <v>5.436748124189239</v>
       </c>
       <c r="AJ91" t="n">
-        <v>9.124950148647669</v>
+        <v>37.0831747153941</v>
       </c>
       <c r="AK91" t="inlineStr"/>
       <c r="AL91" t="inlineStr"/>
@@ -25466,7 +25466,7 @@
         <v>7416.36</v>
       </c>
       <c r="V93" t="n">
-        <v>853.75</v>
+        <v>3212.93</v>
       </c>
       <c r="W93" t="n">
         <v>2089.7</v>
@@ -25508,7 +25508,7 @@
         <v>58.28477679561883</v>
       </c>
       <c r="AJ93" t="n">
-        <v>11.51171194494334</v>
+        <v>43.32219579416318</v>
       </c>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
@@ -25756,7 +25756,7 @@
         <v>8539.940000000001</v>
       </c>
       <c r="V94" t="n">
-        <v>1087.92</v>
+        <v>3917.79</v>
       </c>
       <c r="W94" t="n">
         <v>2539.35</v>
@@ -25798,7 +25798,7 @@
         <v>21.39450475273601</v>
       </c>
       <c r="AJ94" t="n">
-        <v>12.73919957283072</v>
+        <v>45.87608343852533</v>
       </c>
       <c r="AK94" t="inlineStr"/>
       <c r="AL94" t="inlineStr"/>
@@ -26052,7 +26052,7 @@
         <v>10329.75</v>
       </c>
       <c r="V95" t="n">
-        <v>1192.03</v>
+        <v>4200.61</v>
       </c>
       <c r="W95" t="n">
         <v>2689.18</v>
@@ -26094,7 +26094,7 @@
         <v>-2.082592697252272</v>
       </c>
       <c r="AJ95" t="n">
-        <v>11.53977589002638</v>
+        <v>40.66516614632494</v>
       </c>
       <c r="AK95" t="inlineStr"/>
       <c r="AL95" t="inlineStr"/>
@@ -26348,7 +26348,7 @@
         <v>9399.139999999999</v>
       </c>
       <c r="V96" t="n">
-        <v>1015.55</v>
+        <v>4108.07</v>
       </c>
       <c r="W96" t="n">
         <v>2634.45</v>
@@ -26390,7 +26390,7 @@
         <v>-30.35329164791858</v>
       </c>
       <c r="AJ96" t="n">
-        <v>10.8047119204523</v>
+        <v>43.70687105416027</v>
       </c>
       <c r="AK96" t="inlineStr"/>
       <c r="AL96" t="inlineStr"/>
@@ -26650,7 +26650,7 @@
         <v>10884.52</v>
       </c>
       <c r="V97" t="n">
-        <v>1109</v>
+        <v>4506.35</v>
       </c>
       <c r="W97" t="n">
         <v>3012.76</v>
@@ -26692,7 +26692,7 @@
         <v>27.18944929602565</v>
       </c>
       <c r="AJ97" t="n">
-        <v>10.18878186635699</v>
+        <v>41.40145821772573</v>
       </c>
       <c r="AK97" t="inlineStr"/>
       <c r="AL97" t="inlineStr"/>
@@ -27196,7 +27196,7 @@
         <v>7842.66</v>
       </c>
       <c r="V99" t="n">
-        <v>612.3099999999999</v>
+        <v>2388.03</v>
       </c>
       <c r="W99" t="n">
         <v>1591.34</v>
@@ -27238,7 +27238,7 @@
         <v>45.16673477001794</v>
       </c>
       <c r="AJ99" t="n">
-        <v>7.807427581968362</v>
+        <v>30.4492353359702</v>
       </c>
       <c r="AK99" t="inlineStr"/>
       <c r="AL99" t="inlineStr"/>
@@ -27484,7 +27484,7 @@
         <v>7663.23</v>
       </c>
       <c r="V100" t="n">
-        <v>471.91</v>
+        <v>2471.95</v>
       </c>
       <c r="W100" t="n">
         <v>1670.36</v>
@@ -27526,7 +27526,7 @@
         <v>-14.71851670542161</v>
       </c>
       <c r="AJ100" t="n">
-        <v>6.158108265052727</v>
+        <v>32.25728576592377</v>
       </c>
       <c r="AK100" t="inlineStr"/>
       <c r="AL100" t="inlineStr"/>
@@ -27780,7 +27780,7 @@
         <v>8610.23</v>
       </c>
       <c r="V101" t="n">
-        <v>527.88</v>
+        <v>2450.41</v>
       </c>
       <c r="W101" t="n">
         <v>1600.42</v>
@@ -27822,7 +27822,7 @@
         <v>-63.12254694439861</v>
       </c>
       <c r="AJ101" t="n">
-        <v>6.130846678892434</v>
+        <v>28.45928622115785</v>
       </c>
       <c r="AK101" t="inlineStr"/>
       <c r="AL101" t="inlineStr"/>
@@ -28076,7 +28076,7 @@
         <v>9834.110000000001</v>
       </c>
       <c r="V102" t="n">
-        <v>528.42</v>
+        <v>2884.47</v>
       </c>
       <c r="W102" t="n">
         <v>2047.43</v>
@@ -28118,7 +28118,7 @@
         <v>241.2676330382332</v>
       </c>
       <c r="AJ102" t="n">
-        <v>5.373338309211509</v>
+        <v>29.33127654663207</v>
       </c>
       <c r="AK102" t="inlineStr"/>
       <c r="AL102" t="inlineStr"/>
@@ -28382,7 +28382,7 @@
         <v>11245.93</v>
       </c>
       <c r="V103" t="n">
-        <v>552.8099999999999</v>
+        <v>3142.39</v>
       </c>
       <c r="W103" t="n">
         <v>2293.84</v>
@@ -28424,7 +28424,7 @@
         <v>-8.755405671215454</v>
       </c>
       <c r="AJ103" t="n">
-        <v>4.915645037804787</v>
+        <v>27.94246451827461</v>
       </c>
       <c r="AK103" t="inlineStr"/>
       <c r="AL103" t="inlineStr"/>
@@ -28942,7 +28942,7 @@
         <v>6714.07</v>
       </c>
       <c r="V105" t="n">
-        <v>1185.56</v>
+        <v>3994.83</v>
       </c>
       <c r="W105" t="n">
         <v>2509.06</v>
@@ -28984,7 +28984,7 @@
         <v>44.10232791827162</v>
       </c>
       <c r="AJ105" t="n">
-        <v>17.65784390094235</v>
+        <v>59.49937966092102</v>
       </c>
       <c r="AK105" t="inlineStr"/>
       <c r="AL105" t="inlineStr"/>
@@ -29228,7 +29228,7 @@
         <v>7528.72</v>
       </c>
       <c r="V106" t="n">
-        <v>1033.48</v>
+        <v>4245.91</v>
       </c>
       <c r="W106" t="n">
         <v>2702.89</v>
@@ -29270,7 +29270,7 @@
         <v>10.52665221661138</v>
       </c>
       <c r="AJ106" t="n">
-        <v>13.72716743350795</v>
+        <v>56.3961735859482</v>
       </c>
       <c r="AK106" t="inlineStr"/>
       <c r="AL106" t="inlineStr"/>
@@ -29522,7 +29522,7 @@
         <v>12156.97</v>
       </c>
       <c r="V107" t="n">
-        <v>1483.9</v>
+        <v>5394.96</v>
       </c>
       <c r="W107" t="n">
         <v>3287.89</v>
@@ -29564,7 +29564,7 @@
         <v>-85.2672421951399</v>
       </c>
       <c r="AJ107" t="n">
-        <v>12.20616650366004</v>
+        <v>44.37750525007465</v>
       </c>
       <c r="AK107" t="inlineStr"/>
       <c r="AL107" t="inlineStr"/>
@@ -29816,7 +29816,7 @@
         <v>14538.48</v>
       </c>
       <c r="V108" t="n">
-        <v>1564.3</v>
+        <v>6668.56</v>
       </c>
       <c r="W108" t="n">
         <v>4435.46</v>
@@ -29858,7 +29858,7 @@
         <v>82.30675897509099</v>
       </c>
       <c r="AJ108" t="n">
-        <v>10.75972178659667</v>
+        <v>45.86834387088609</v>
       </c>
       <c r="AK108" t="inlineStr"/>
       <c r="AL108" t="inlineStr"/>
@@ -30124,7 +30124,7 @@
         <v>10572.63</v>
       </c>
       <c r="V109" t="n">
-        <v>1465.48</v>
+        <v>6309.94</v>
       </c>
       <c r="W109" t="n">
         <v>4129.92</v>
@@ -30166,7 +30166,7 @@
         <v>70.75715460204361</v>
       </c>
       <c r="AJ109" t="n">
-        <v>13.86107335639288</v>
+        <v>59.68183886128617</v>
       </c>
       <c r="AK109" t="inlineStr"/>
       <c r="AL109" t="inlineStr"/>
@@ -30682,7 +30682,7 @@
         <v>9723.93</v>
       </c>
       <c r="V111" t="n">
-        <v>1234.09</v>
+        <v>4503.54</v>
       </c>
       <c r="W111" t="n">
         <v>3031.78</v>
@@ -30724,7 +30724,7 @@
         <v>-21.78661829612639</v>
       </c>
       <c r="AJ111" t="n">
-        <v>12.69126783101071</v>
+        <v>46.31399033106985</v>
       </c>
       <c r="AK111" t="inlineStr"/>
       <c r="AL111" t="inlineStr"/>
@@ -31264,7 +31264,7 @@
         <v>13268.39</v>
       </c>
       <c r="V113" t="n">
-        <v>1165.72</v>
+        <v>5697.52</v>
       </c>
       <c r="W113" t="n">
         <v>3967.26</v>
@@ -31306,7 +31306,7 @@
         <v>-16.25248671036753</v>
       </c>
       <c r="AJ113" t="n">
-        <v>8.785692913759696</v>
+        <v>42.94055269704916</v>
       </c>
       <c r="AK113" t="inlineStr"/>
       <c r="AL113" t="inlineStr"/>
@@ -31558,7 +31558,7 @@
         <v>11544.86</v>
       </c>
       <c r="V114" t="n">
-        <v>1345.48</v>
+        <v>6308.12</v>
       </c>
       <c r="W114" t="n">
         <v>4349.26</v>
@@ -31600,7 +31600,7 @@
         <v>-29.00201105384229</v>
       </c>
       <c r="AJ114" t="n">
-        <v>11.6543639333868</v>
+        <v>54.64007359119123</v>
       </c>
       <c r="AK114" t="inlineStr"/>
       <c r="AL114" t="inlineStr"/>
@@ -31848,7 +31848,7 @@
         <v>12932.4</v>
       </c>
       <c r="V115" t="n">
-        <v>1372.03</v>
+        <v>6755.95</v>
       </c>
       <c r="W115" t="n">
         <v>4801.53</v>
@@ -31890,7 +31890,7 @@
         <v>11.10806395373893</v>
       </c>
       <c r="AJ115" t="n">
-        <v>10.60924499706164</v>
+        <v>52.24049673687792</v>
       </c>
       <c r="AK115" t="inlineStr"/>
       <c r="AL115" t="inlineStr"/>
@@ -32386,7 +32386,7 @@
         <v>5817.55</v>
       </c>
       <c r="V117" t="n">
-        <v>656.14</v>
+        <v>2258.32</v>
       </c>
       <c r="W117" t="n">
         <v>1439.2</v>
@@ -32428,7 +32428,7 @@
         <v>30.48877979575064</v>
       </c>
       <c r="AJ117" t="n">
-        <v>11.27863103883937</v>
+        <v>38.81909051061014</v>
       </c>
       <c r="AK117" t="inlineStr"/>
       <c r="AL117" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
         <v>6029.7</v>
       </c>
       <c r="V118" t="n">
-        <v>625.4299999999999</v>
+        <v>2520.75</v>
       </c>
       <c r="W118" t="n">
         <v>1549.41</v>
@@ -32720,7 +32720,7 @@
         <v>-9.694454271686336</v>
       </c>
       <c r="AJ118" t="n">
-        <v>10.37248951025756</v>
+        <v>41.80556246579432</v>
       </c>
       <c r="AK118" t="inlineStr"/>
       <c r="AL118" t="inlineStr"/>
@@ -32976,7 +32976,7 @@
         <v>7651.8</v>
       </c>
       <c r="V119" t="n">
-        <v>704.6799999999999</v>
+        <v>2828.37</v>
       </c>
       <c r="W119" t="n">
         <v>1761.95</v>
@@ -33018,7 +33018,7 @@
         <v>24.4931012077664</v>
       </c>
       <c r="AJ119" t="n">
-        <v>9.209336365299666</v>
+        <v>36.96345957813848</v>
       </c>
       <c r="AK119" t="inlineStr"/>
       <c r="AL119" t="inlineStr"/>
@@ -33274,7 +33274,7 @@
         <v>7929.03</v>
       </c>
       <c r="V120" t="n">
-        <v>749.84</v>
+        <v>3024.82</v>
       </c>
       <c r="W120" t="n">
         <v>1913.49</v>
@@ -33316,7 +33316,7 @@
         <v>-7.995655827983061</v>
       </c>
       <c r="AJ120" t="n">
-        <v>9.456894475112341</v>
+        <v>38.14867644592088</v>
       </c>
       <c r="AK120" t="inlineStr"/>
       <c r="AL120" t="inlineStr"/>
@@ -33582,7 +33582,7 @@
         <v>8602.459999999999</v>
       </c>
       <c r="V121" t="n">
-        <v>782.08</v>
+        <v>3137.45</v>
       </c>
       <c r="W121" t="n">
         <v>2001.7</v>
@@ -33624,7 +33624,7 @@
         <v>7.300286972770964</v>
       </c>
       <c r="AJ121" t="n">
-        <v>9.091352938578035</v>
+        <v>36.4715441861979</v>
       </c>
       <c r="AK121" t="inlineStr"/>
       <c r="AL121" t="inlineStr"/>
@@ -34136,7 +34136,7 @@
         <v>4225.28</v>
       </c>
       <c r="V123" t="n">
-        <v>740.91</v>
+        <v>2494.27</v>
       </c>
       <c r="W123" t="n">
         <v>1567.06</v>
@@ -34178,7 +34178,7 @@
         <v>-37.57216444746817</v>
       </c>
       <c r="AJ123" t="n">
-        <v>17.53516926688882</v>
+        <v>59.03206414722811</v>
       </c>
       <c r="AK123" t="inlineStr"/>
       <c r="AL123" t="inlineStr"/>
@@ -34422,7 +34422,7 @@
         <v>5787.02</v>
       </c>
       <c r="V124" t="n">
-        <v>615.91</v>
+        <v>2798.42</v>
       </c>
       <c r="W124" t="n">
         <v>1828.05</v>
@@ -34464,7 +34464,7 @@
         <v>70.0408934279902</v>
       </c>
       <c r="AJ124" t="n">
-        <v>10.64295613286285</v>
+        <v>48.35683996253685</v>
       </c>
       <c r="AK124" t="inlineStr"/>
       <c r="AL124" t="inlineStr"/>
@@ -34714,7 +34714,7 @@
         <v>7334.88</v>
       </c>
       <c r="V125" t="n">
-        <v>701.8099999999999</v>
+        <v>3012.13</v>
       </c>
       <c r="W125" t="n">
         <v>1976.67</v>
@@ -34756,7 +34756,7 @@
         <v>20.0938772271426</v>
       </c>
       <c r="AJ125" t="n">
-        <v>9.568118360491242</v>
+        <v>41.06583884126257</v>
       </c>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
@@ -35004,7 +35004,7 @@
         <v>6409.65</v>
       </c>
       <c r="V126" t="n">
-        <v>691.23</v>
+        <v>2924.99</v>
       </c>
       <c r="W126" t="n">
         <v>1968.21</v>
@@ -35046,7 +35046,7 @@
         <v>1.639635884951018</v>
       </c>
       <c r="AJ126" t="n">
-        <v>10.78420818609441</v>
+        <v>45.63416099162981</v>
       </c>
       <c r="AK126" t="inlineStr"/>
       <c r="AL126" t="inlineStr"/>
@@ -35308,7 +35308,7 @@
         <v>6803.59</v>
       </c>
       <c r="V127" t="n">
-        <v>761.53</v>
+        <v>3027.82</v>
       </c>
       <c r="W127" t="n">
         <v>1983.26</v>
@@ -35350,7 +35350,7 @@
         <v>-9.441585782364969</v>
       </c>
       <c r="AJ127" t="n">
-        <v>11.19306131027884</v>
+        <v>44.50326959737433</v>
       </c>
       <c r="AK127" t="inlineStr"/>
       <c r="AL127" t="inlineStr"/>
@@ -35862,7 +35862,7 @@
         <v>8462.82</v>
       </c>
       <c r="V129" t="n">
-        <v>932.14</v>
+        <v>3503.02</v>
       </c>
       <c r="W129" t="n">
         <v>2368.24</v>
@@ -35904,7 +35904,7 @@
         <v>33.17860991504984</v>
       </c>
       <c r="AJ129" t="n">
-        <v>11.01453179909297</v>
+        <v>41.39305810592687</v>
       </c>
       <c r="AK129" t="inlineStr"/>
       <c r="AL129" t="inlineStr"/>
@@ -36152,7 +36152,7 @@
         <v>8791.969999999999</v>
       </c>
       <c r="V130" t="n">
-        <v>827.86</v>
+        <v>3917.95</v>
       </c>
       <c r="W130" t="n">
         <v>2685.02</v>
@@ -36194,7 +36194,7 @@
         <v>1.66840057026163</v>
       </c>
       <c r="AJ130" t="n">
-        <v>9.416092184118007</v>
+        <v>44.56282266659235</v>
       </c>
       <c r="AK130" t="inlineStr"/>
       <c r="AL130" t="inlineStr"/>
@@ -36448,7 +36448,7 @@
         <v>10058.23</v>
       </c>
       <c r="V131" t="n">
-        <v>917.4400000000001</v>
+        <v>4217.69</v>
       </c>
       <c r="W131" t="n">
         <v>2852.24</v>
@@ -36490,7 +36490,7 @@
         <v>9.106413180543393</v>
       </c>
       <c r="AJ131" t="n">
-        <v>9.121286747270645</v>
+        <v>41.93272573802746</v>
       </c>
       <c r="AK131" t="inlineStr"/>
       <c r="AL131" t="inlineStr"/>
@@ -36744,7 +36744,7 @@
         <v>9977.299999999999</v>
       </c>
       <c r="V132" t="n">
-        <v>985.63</v>
+        <v>4441.68</v>
       </c>
       <c r="W132" t="n">
         <v>2977.9</v>
@@ -36786,7 +36786,7 @@
         <v>-2.739068514606358</v>
       </c>
       <c r="AJ132" t="n">
-        <v>9.878724705080534</v>
+        <v>44.51785553205777</v>
       </c>
       <c r="AK132" t="inlineStr"/>
       <c r="AL132" t="inlineStr"/>
@@ -37046,7 +37046,7 @@
         <v>11155.79</v>
       </c>
       <c r="V133" t="n">
-        <v>1065.58</v>
+        <v>4805.62</v>
       </c>
       <c r="W133" t="n">
         <v>3240.21</v>
@@ -37088,7 +37088,7 @@
         <v>9.303805482414141</v>
       </c>
       <c r="AJ133" t="n">
-        <v>9.551811211935684</v>
+        <v>43.07736162118505</v>
       </c>
       <c r="AK133" t="inlineStr"/>
       <c r="AL133" t="inlineStr"/>
@@ -37884,7 +37884,7 @@
         <v>5333.47</v>
       </c>
       <c r="V136" t="n">
-        <v>542.0700000000001</v>
+        <v>1958.71</v>
       </c>
       <c r="W136" t="n">
         <v>1268</v>
@@ -37926,7 +37926,7 @@
         <v>61.27148208515627</v>
       </c>
       <c r="AJ136" t="n">
-        <v>10.16355205897849</v>
+        <v>36.72487142516973</v>
       </c>
       <c r="AK136" t="inlineStr"/>
       <c r="AL136" t="inlineStr"/>
@@ -38180,7 +38180,7 @@
         <v>7842.55</v>
       </c>
       <c r="V137" t="n">
-        <v>571.03</v>
+        <v>2272.6</v>
       </c>
       <c r="W137" t="n">
         <v>1542.79</v>
@@ -38222,7 +38222,7 @@
         <v>53.6098194536178</v>
       </c>
       <c r="AJ137" t="n">
-        <v>7.281177678178653</v>
+        <v>28.9778197142511</v>
       </c>
       <c r="AK137" t="inlineStr"/>
       <c r="AL137" t="inlineStr"/>
@@ -38474,7 +38474,7 @@
         <v>7230.98</v>
       </c>
       <c r="V138" t="n">
-        <v>553.2</v>
+        <v>2300.83</v>
       </c>
       <c r="W138" t="n">
         <v>1597.87</v>
@@ -38516,7 +38516,7 @@
         <v>-5.484614740876048</v>
       </c>
       <c r="AJ138" t="n">
-        <v>7.650415296405192</v>
+        <v>31.81906186989869</v>
       </c>
       <c r="AK138" t="inlineStr"/>
       <c r="AL138" t="inlineStr"/>
@@ -38780,7 +38780,7 @@
         <v>6574.71</v>
       </c>
       <c r="V139" t="n">
-        <v>534.29</v>
+        <v>2223.24</v>
       </c>
       <c r="W139" t="n">
         <v>1550.28</v>
@@ -38822,7 +38822,7 @@
         <v>-8.021018114537126</v>
       </c>
       <c r="AJ139" t="n">
-        <v>8.126442078814122</v>
+        <v>33.81502758296563</v>
       </c>
       <c r="AK139" t="inlineStr"/>
       <c r="AL139" t="inlineStr"/>
